--- a/out/MLP-S4_repeat_4_000008.xlsx
+++ b/out/MLP-S4_repeat_4_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.901262215535431</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.50126221553543</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.50126221553543</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.50126221553543</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5903981995424215</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.50126221553543</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.50126221553543</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5903981995424215</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.50126221553543</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.50126221553543</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.50126221553543</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.50126221553543</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.50126221553543</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.50126221553543</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.50126221553543</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.50126221553543</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.50126221553543</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.901262215535431</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.901262215535431</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.901262215535431</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.901262215535431</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.901262215535431</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.901262215535431</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.901262215535431</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001433671547091799</v>
+        <v>-0.0001400802099283319</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1647013245604964</v>
+        <v>-0.1609252563232461</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.901262215535431</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.901262215535431</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.901262215535431</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5903981995424215</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.50126221553543</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1649809006365577</v>
+        <v>-0.1611864152315984</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4897762608800085</v>
+        <v>0.4353711682502186</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8155120094793413</v>
+        <v>0.7103923643335108</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03489641917000869</v>
+        <v>0.03102010432907314</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5903981995424215</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3947430053930862</v>
+        <v>0.3363625806186774</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06119642927740337</v>
+        <v>0.05439882210839907</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.50126221553543</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.482227982774931</v>
+        <v>0.4141296951803143</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07434674611763464</v>
+        <v>0.06608814441179658</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5697189661962949</v>
+        <v>0.4919019858187302</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01967384678206206</v>
+        <v>0.01748841384980207</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5346253229143662</v>
+        <v>0.4607066224258325</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0109303707166635</v>
+        <v>0.009715655634874901</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.50126221553543</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5367927952648932</v>
+        <v>0.4626327737459778</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02296414141173278</v>
+        <v>0.02041393983913546</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.50126221553543</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5718066936483917</v>
+        <v>0.4937572820178666</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.009019920648391633</v>
+        <v>0.00801715168745923</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.50126221553543</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5668602764824829</v>
+        <v>0.4893599112037255</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006422108313655874</v>
+        <v>0.00570798516769411</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5706808120660239</v>
+        <v>0.4927553872779843</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002524751303449343</v>
+        <v>0.002243667825288305</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5693032042743011</v>
+        <v>0.4915302914631194</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001430055658485816</v>
+        <v>0.00127129010228384</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5696386326068565</v>
+        <v>0.4918278935260622</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005422560614976823</v>
+        <v>0.0004811888615022328</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5692903992145001</v>
+        <v>0.4915179608555997</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002515237833159681</v>
+        <v>0.0002228988117871476</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5692508014455945</v>
+        <v>0.4914822237819368</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.864973414506104e-05</v>
+        <v>7.815450531845937e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5691771698398495</v>
+        <v>0.4914162507023255</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.266517359622213e-05</v>
+        <v>1.980325908626812e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5691334304887217</v>
+        <v>0.4913768153925931</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>8.832586798111064e-06</v>
+        <v>7.401629543134059e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5691284088941025</v>
+        <v>0.4913717960319002</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.705352179376644e-06</v>
+        <v>1.677971888793091e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5691244995177537</v>
+        <v>0.4913677412390646</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5691222485900221</v>
+        <v>0.4913651238356458</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5691166569300138</v>
+        <v>0.4913596065936561</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5691103329360059</v>
+        <v>0.4913532825996482</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5691049651474275</v>
+        <v>0.4913479148110698</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5691050018959192</v>
+        <v>0.4913479515595615</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5691051121413948</v>
+        <v>0.4913480618050371</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5691051856383784</v>
+        <v>0.4913481353020207</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5691053693808376</v>
+        <v>0.4913483190444798</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.50126221553543</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.569106912817494</v>
+        <v>0.4913498624811363</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5903981995424215</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5691083827571671</v>
+        <v>0.4913513324208094</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5903981995424215</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5691096322058891</v>
+        <v>0.4913525818695314</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.50126221553543</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5691109919000864</v>
+        <v>0.4913539415637287</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.50126221553543</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5691087869905771</v>
+        <v>0.4913517366542194</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.50126221553543</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5691083827571671</v>
+        <v>0.4913513324208094</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5903981995424215</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5691075375418552</v>
+        <v>0.4913504872054975</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5691080887692324</v>
+        <v>0.4913510384328747</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.569107758032806</v>
+        <v>0.4913507076964483</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5691074640448716</v>
+        <v>0.4913504137085138</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5691075375418552</v>
+        <v>0.4913504872054975</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5691070965599532</v>
+        <v>0.4913500462235955</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5691069863144776</v>
+        <v>0.4913499359781199</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.569106949565986</v>
+        <v>0.4913498992296282</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5691070965599532</v>
+        <v>0.4913500462235955</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.50126221553543</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5691066188295595</v>
+        <v>0.4913495684932019</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.50126221553543</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5691075742903469</v>
+        <v>0.4913505239539891</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5691075375418552</v>
+        <v>0.4913504872054975</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5691072068054287</v>
+        <v>0.491350156469071</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5691076477873307</v>
+        <v>0.491350597450973</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5691070230629696</v>
+        <v>0.4913499727266119</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5691068393205104</v>
+        <v>0.4913497889841527</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5691064350871003</v>
+        <v>0.4913493847507427</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5691055898717884</v>
+        <v>0.4913485395354307</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5691055531232967</v>
+        <v>0.491348502786939</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5691057001172639</v>
+        <v>0.4913486497809063</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5691056266202803</v>
+        <v>0.4913485762839226</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5691057001172639</v>
+        <v>0.4913486497809063</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5691057368657558</v>
+        <v>0.4913486865293982</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5691056266202803</v>
+        <v>0.4913485762839226</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5691060676021823</v>
+        <v>0.4913490172658246</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5691059573567068</v>
+        <v>0.4913489070203491</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5691059206082149</v>
+        <v>0.4913488702718571</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5691058471112311</v>
+        <v>0.4913487967748735</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5691058103627394</v>
+        <v>0.4913487600263818</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5691055898717884</v>
+        <v>0.4913485395354307</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5691055163748048</v>
+        <v>0.4913484660384471</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5691054428778212</v>
+        <v>0.4913483925414635</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5691054796263131</v>
+        <v>0.4913484292899554</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5691053693808376</v>
+        <v>0.4913483190444798</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5691054796263131</v>
+        <v>0.4913484292899554</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5691057736142475</v>
+        <v>0.4913487232778899</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_4_000008.xlsx
+++ b/out/MLP-S4_repeat_4_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.4094390911976031</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.901262215535431</v>
+        <v>0.7627717100636433</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636436</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.4505587654005176</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.4505587654005176</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4505587654005176</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.4505587654005176</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4505587654005176</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.901262215535431</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001433671547091799</v>
+        <v>-0.0001335170804352965</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1647013245604964</v>
+        <v>-0.1533854811009641</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1535189981813994</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.901262215535431</v>
+        <v>0.7627717100636435</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1535189981813994</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1535189981813994</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1535189981813994</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1535189981813994</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1535189981813994</v>
       </c>
     </row>
     <row r="52">
@@ -42277,17 +42277,17 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1535189981813994</v>
       </c>
     </row>
     <row r="53">
@@ -43072,17 +43072,17 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.901262215535431</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1535189981813994</v>
       </c>
     </row>
     <row r="54">
@@ -43867,17 +43867,17 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1535189981813994</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1535189981813994</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1535189981813994</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1535189981813994</v>
       </c>
     </row>
     <row r="58">
@@ -47047,17 +47047,17 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1648446917152055</v>
+        <v>-0.1535189981813994</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1649809006365577</v>
+        <v>-0.1536091147633725</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4897762608800085</v>
+        <v>0.3240387055699677</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8155120094793413</v>
+        <v>0.4950904625571484</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03489641917000869</v>
+        <v>0.02308768973801508</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3947430053930862</v>
+        <v>0.2167073428125072</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06119642927740337</v>
+        <v>0.04048794133712602</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.482227982774931</v>
+        <v>0.2745878308505555</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07434674611763464</v>
+        <v>0.04918806713668161</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5697189661962949</v>
+        <v>0.3324721713376986</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01967384678206206</v>
+        <v>0.01301622996803596</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5346253229143662</v>
+        <v>0.3092540943803589</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0109303707166635</v>
+        <v>0.007229727095400554</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5367927952648932</v>
+        <v>0.310686416154261</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02296414141173278</v>
+        <v>0.01519333382671337</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5718066936483917</v>
+        <v>0.3338524087789496</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.009019920648391633</v>
+        <v>0.005965592967870472</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5668602764824829</v>
+        <v>0.3305779977113465</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006422108313655874</v>
+        <v>0.004246965108202288</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5706808120660239</v>
+        <v>0.3331043616839058</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002524751303449343</v>
+        <v>0.001669279848176618</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5693032042743011</v>
+        <v>0.3321909207782729</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001430055658485816</v>
+        <v>0.000944510510877833</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5696386326068565</v>
+        <v>0.3324112287607954</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005422560614976823</v>
+        <v>0.0003567057230499703</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5692903992145001</v>
+        <v>0.3321790031538906</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002515237833159681</v>
+        <v>0.0001645479082860905</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5692508014455945</v>
+        <v>0.3321510624620079</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.864973414506104e-05</v>
+        <v>5.716404766525603e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5691771698398495</v>
+        <v>0.3321004064346645</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.266517359622213e-05</v>
+        <v>1.360244431470109e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5691334304887217</v>
+        <v>0.3320695799523652</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>8.832586798111064e-06</v>
+        <v>4.062729281521043e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5691284088941025</v>
+        <v>0.3320645658041663</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.705352179376644e-06</v>
+        <v>1.369014529177619e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5691244995177537</v>
+        <v>0.3320602928866006</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5691222485900221</v>
+        <v>0.3320571252650358</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5691166569300138</v>
+        <v>0.332051755938048</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5691103329360059</v>
+        <v>0.3320457632046176</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5691049651474275</v>
+        <v>0.3320403954160393</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5691050018959192</v>
+        <v>0.3320404321645309</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5691051121413948</v>
+        <v>0.3320405424100065</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5691051856383784</v>
+        <v>0.3320406159069901</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5691053693808376</v>
+        <v>0.3320407996494493</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.569106912817494</v>
+        <v>0.3320423430861058</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5691083827571671</v>
+        <v>0.3320438130257788</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5691096322058891</v>
+        <v>0.3320450624745008</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5691109919000864</v>
+        <v>0.3320464221686982</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5691087869905771</v>
+        <v>0.3320442172591889</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5691083827571671</v>
+        <v>0.3320438130257788</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5691075375418552</v>
+        <v>0.3320429678104669</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5691080887692324</v>
+        <v>0.3320435190378441</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.569107758032806</v>
+        <v>0.3320431883014178</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5691074640448716</v>
+        <v>0.3320428943134833</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5691075375418552</v>
+        <v>0.3320429678104669</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5691070965599532</v>
+        <v>0.3320425268285649</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5691069863144776</v>
+        <v>0.3320424165830894</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.569106949565986</v>
+        <v>0.3320423798345977</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5691070965599532</v>
+        <v>0.3320425268285649</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5691066188295595</v>
+        <v>0.3320420490981713</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5691075742903469</v>
+        <v>0.3320430045589586</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5691075375418552</v>
+        <v>0.3320429678104669</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.4505587654005176</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5691072068054287</v>
+        <v>0.3320426370740405</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5691076477873307</v>
+        <v>0.3320430780559424</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5691070230629696</v>
+        <v>0.3320424533315813</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5691068393205104</v>
+        <v>0.3320422695891221</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5691064350871003</v>
+        <v>0.3320418653557121</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5691055898717884</v>
+        <v>0.3320410201404002</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5691055531232967</v>
+        <v>0.3320409833919085</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5691057001172639</v>
+        <v>0.3320411303858757</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5691056266202803</v>
+        <v>0.3320410568888921</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5691057001172639</v>
+        <v>0.3320411303858757</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5691057368657558</v>
+        <v>0.3320411671343677</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5691056266202803</v>
+        <v>0.3320410568888921</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5691060676021823</v>
+        <v>0.332041497870794</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5691059573567068</v>
+        <v>0.3320413876253185</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5691059206082149</v>
+        <v>0.3320413508768266</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5691058471112311</v>
+        <v>0.332041277379843</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5691058103627394</v>
+        <v>0.3320412406313513</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5691055898717884</v>
+        <v>0.3320410201404002</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5691055163748048</v>
+        <v>0.3320409466434165</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5691054428778212</v>
+        <v>0.3320408731464329</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5691054796263131</v>
+        <v>0.3320409098949249</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5691053693808376</v>
+        <v>0.3320407996494493</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5691054796263131</v>
+        <v>0.3320409098949249</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5691057736142475</v>
+        <v>0.3320412038828593</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_4_000008.xlsx
+++ b/out/MLP-S4_repeat_4_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4573243260383606</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.4094390911976031</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5228384733200073</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.7627717100636433</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.6191324591636658</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.669436947795724</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.6641244888305664</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.669436947795724</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.5273509621620178</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.9627717100636436</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4508839845657349</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.256106472331563</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.46135014295578</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4505587654005176</v>
+        <v>0.16</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4282100796699524</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4518122375011444</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4418096542358398</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4736111462116241</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4661439955234528</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.473279595375061</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.47078937292099</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.05610647233156292</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.5449051260948181</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.256106472331563</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4910925328731537</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.256106472331563</v>
+        <v>0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4462335109710693</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4505587654005176</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4429120123386383</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.4505587654005176</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4648719131946564</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4657913148403168</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4650329351425171</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4916795194149017</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4789408147335052</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.5248594880104065</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.256106472331563</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4990701079368591</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.256106472331563</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4967155754566193</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4505587654005176</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.4951660335063934</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4505587654005176</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4959088563919067</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.05610647233156292</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.5167442560195923</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.5479300022125244</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.669436947795724</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.6779744625091553</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.669436947795724</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.5495490431785583</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.669436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.5436321496963501</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.669436947795724</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.538618266582489</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.669436947795724</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.5175432562828064</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.669436947795724</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.5594415664672852</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.669436947795724</v>
+        <v>-0.16</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.5172809958457947</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.669436947795724</v>
+        <v>-0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.5164133310317993</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.669436947795724</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.5868627429008484</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.469436947795724</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5949281454086304</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.469436947795724</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5825812816619873</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.469436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.6365509033203125</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.469436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.7117117643356323</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.469436947795724</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.6919230222702026</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.469436947795724</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001335170804352965</v>
+        <v>-0.0001164229180378607</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1533854811009641</v>
+        <v>-0.1337475717430304</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.5213371515274048</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.469436947795724</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1535189981813994</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5908634662628174</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.7627717100636435</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1535189981813994</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.4617162048816681</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1535189981813994</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4981396496295929</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1535189981813994</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4555582702159882</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1535189981813994</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.455555647611618</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1535189981813994</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="52">
@@ -42277,17 +42277,17 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4533499479293823</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1535189981813994</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="53">
@@ -43072,17 +43072,17 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5081310272216797</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1535189981813994</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="54">
@@ -43867,17 +43867,17 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.4630635976791382</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1535189981813994</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4715596139431</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1535189981813994</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.468037873506546</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1535189981813994</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.465241014957428</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1535189981813994</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="58">
@@ -47047,17 +47047,17 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.4971692860126495</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1535189981813994</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.5929520130157471</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1536091147633725</v>
+        <v>-0.1339479864948697</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3240387055699677</v>
+        <v>0.3020155059984765</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.4690560698509216</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.256106472331563</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4950904625571484</v>
+        <v>0.4706629063330298</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02308768973801508</v>
+        <v>0.0215185048061819</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.485004335641861</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.256106472331563</v>
+        <v>0.16</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2167073428125072</v>
+        <v>0.2112000172603822</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04048794133712602</v>
+        <v>0.03773625394081598</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.5602790117263794</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2745878308505555</v>
+        <v>0.2651467659141433</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.04918806713668161</v>
+        <v>0.04584509192186752</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.4533684849739075</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.256106472331563</v>
+        <v>0.16</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3324721713376986</v>
+        <v>0.3190971051924834</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01301622996803596</v>
+        <v>0.01213175998034995</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3790187537670135</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.256106472331563</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3092540943803589</v>
+        <v>0.297457001187531</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007229727095400554</v>
+        <v>0.006738117850581246</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.6279742121696472</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.310686416154261</v>
+        <v>0.298791620800464</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01519333382671337</v>
+        <v>0.01416058700481702</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.6105940341949463</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.669436947795724</v>
+        <v>0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3338524087789496</v>
+        <v>0.3203820178820475</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.005965592967870472</v>
+        <v>0.005559883303725115</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.5464727878570557</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3305779977113465</v>
+        <v>0.3173300758695204</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004246965108202288</v>
+        <v>0.003957176005493167</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4347941875457764</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.256106472331563</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3331043616839058</v>
+        <v>0.3196839519252695</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001669279848176618</v>
+        <v>0.001555216987473588</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.4566066861152649</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3321909207782729</v>
+        <v>0.3188323999377817</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.000944510510877833</v>
+        <v>0.0008797711578634354</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.3853607475757599</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3324112287607954</v>
+        <v>0.3190373585403</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003567057230499703</v>
+        <v>0.0003320439692056542</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.357843279838562</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3321790031538906</v>
+        <v>0.3188206005326216</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001645479082860905</v>
+        <v>0.0001535383038519288</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.3062852025032043</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3321510624620079</v>
+        <v>0.3187942182205084</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.716404766525603e-05</v>
+        <v>5.312742119348616e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.3244791328907013</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3321004064346645</v>
+        <v>0.318746801768074</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.360244431470109e-05</v>
+        <v>1.217148705972408e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.3596905469894409</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3320695799523652</v>
+        <v>0.3187179619382594</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>4.062729281521043e-06</v>
+        <v>3.58574352986204e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.3476093113422394</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3320645658041663</v>
+        <v>0.3187129485347029</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.369014529177619e-07</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.3865632712841034</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3320602928866006</v>
+        <v>0.3187086029088935</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.513939432721747e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.337772935628891</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3320571252650358</v>
+        <v>0.3187052525541007</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.3464900851249695</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.332051755938048</v>
+        <v>0.318699883227113</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.346753716468811</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3320457632046176</v>
+        <v>0.3186938904936826</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.3722661435604095</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3320403954160393</v>
+        <v>0.3186885227051042</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.383974015712738</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3320404321645309</v>
+        <v>0.3186885594535959</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.3841838836669922</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3320405424100065</v>
+        <v>0.3186886696990714</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.3710956573486328</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.16</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3320406159069901</v>
+        <v>0.3186887431960551</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4600018262863159</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.256106472331563</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3320407996494493</v>
+        <v>0.3186889269385142</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.6224683523178101</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.256106472331563</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3320423430861058</v>
+        <v>0.3186904703751707</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.4471520483493805</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.256106472331563</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3320438130257788</v>
+        <v>0.3186919403148438</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.4662351906299591</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.256106472331563</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3320450624745008</v>
+        <v>0.3186931897635658</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.9790098667144775</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3320464221686982</v>
+        <v>0.3186945494577631</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.636861264705658</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.669436947795724</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3320442172591889</v>
+        <v>0.3186923445482538</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.5372135639190674</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3320438130257788</v>
+        <v>0.3186919403148438</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.4683960676193237</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3320429678104669</v>
+        <v>0.3186910950995318</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.3312561213970184</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3320435190378441</v>
+        <v>0.3186916463269091</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.2451239377260208</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3320431883014178</v>
+        <v>0.3186913155904827</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.306795746088028</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3320428943134833</v>
+        <v>0.3186910216025482</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.2791495025157928</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3320429678104669</v>
+        <v>0.3186910950995318</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.258134126663208</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3320425268285649</v>
+        <v>0.3186906541176299</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.2806866765022278</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3320424165830894</v>
+        <v>0.3186905438721543</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.2992871999740601</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3320423798345977</v>
+        <v>0.3186905071236626</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.2990118265151978</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3320425268285649</v>
+        <v>0.3186906541176299</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.6361395120620728</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3320420490981713</v>
+        <v>0.3186901763872362</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.6684093475341797</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3320430045589586</v>
+        <v>0.3186911318480235</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.32732954621315</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.256106472331563</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3320429678104669</v>
+        <v>0.3186910950995318</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.4141745269298553</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4505587654005176</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3320426370740405</v>
+        <v>0.3186907643631054</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.2920631170272827</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3320430780559424</v>
+        <v>0.3186912053450073</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.30661940574646</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3320424533315813</v>
+        <v>0.3186905806206463</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3286214768886566</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3320422695891221</v>
+        <v>0.3186903968781871</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.2524256110191345</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3320418653557121</v>
+        <v>0.318689992644777</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3138117492198944</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3320410201404002</v>
+        <v>0.3186891474294651</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.2651845812797546</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3320409833919085</v>
+        <v>0.3186891106809734</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3094320595264435</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3320411303858757</v>
+        <v>0.3186892576749406</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3230431377887726</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3320410568888921</v>
+        <v>0.318689184177957</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.4433851838111877</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3320411303858757</v>
+        <v>0.3186892576749406</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.2739336490631104</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3320411671343677</v>
+        <v>0.3186892944234326</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.3714093863964081</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3320410568888921</v>
+        <v>0.318689184177957</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.2551809847354889</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.332041497870794</v>
+        <v>0.3186896251598589</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.2541072964668274</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3320413876253185</v>
+        <v>0.3186895149143834</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.2298413962125778</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3320413508768266</v>
+        <v>0.3186894781658915</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.2530474662780762</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.332041277379843</v>
+        <v>0.3186894046689079</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.2859313189983368</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3320412406313513</v>
+        <v>0.3186893679204162</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.2343643605709076</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3320410201404002</v>
+        <v>0.3186891474294651</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.2787663638591766</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3320409466434165</v>
+        <v>0.3186890739324815</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3588752746582031</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3320408731464329</v>
+        <v>0.3186890004354979</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3400584161281586</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3320409098949249</v>
+        <v>0.3186890371839898</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3874001801013947</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3320407996494493</v>
+        <v>0.3186889269385142</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4566861093044281</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3320409098949249</v>
+        <v>0.3186890371839898</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4747157096862793</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3320412038828593</v>
+        <v>0.3186893311719243</v>
       </c>
     </row>
   </sheetData>
